--- a/Mantenimiento/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/Mantenimiento/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1575,11 +1470,6 @@
       </c>
       <c r="K22" t="n">
         <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/CALLAO-CALLAO-VENTANILLA.xlsx
+++ b/Mantenimiento/excels/CALLAO-CALLAO-VENTANILLA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -508,28 +496,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>144348</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93 VIRGEN MARIA AUXILIADORA</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>-11.875157</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.10725499999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>339</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+          <t>104 MI PEQUEÑO GRAN MUNDO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.890433</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.127141</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -555,28 +553,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>144372</t>
+          <t>144541</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104 MI PEQUEÑO GRAN MUNDO</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>-11.890433</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.12714099999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>264</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+          <t>5052 VIRGEN DE LA MERCED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.875876</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.124247</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -602,28 +610,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>144517</t>
+          <t>144598</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4020 JOSE SANTOS CHOCANO</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>-11.8709</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.1148</v>
-      </c>
-      <c r="I4" t="n">
-        <v>770</v>
-      </c>
-      <c r="J4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+          <t>5088 HEROES DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.889443</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.130086</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -649,28 +667,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>144541</t>
+          <t>144616</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5052 VIRGEN DE LA MERCED</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-11.875876</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.124247</v>
-      </c>
-      <c r="I5" t="n">
-        <v>931</v>
-      </c>
-      <c r="J5" t="n">
-        <v>37</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+          <t>5091 HIJOS DE GRAU</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.886214</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.132396</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -696,28 +724,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>144560</t>
+          <t>144621</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5077 JOSE FAUSTINO SANCHEZ CARRION</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>-11.8308</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.1225</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1304</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+          <t>5093 ANTONIO RAYMONDI</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.885733</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.12378</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -743,28 +781,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>144598</t>
+          <t>144635</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5088 HEROES DEL PACIFICO</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>-11.889443</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.13008600000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1364</v>
-      </c>
-      <c r="J7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+          <t>5094 NACIONES UNIDAS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.827088</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.129217</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -790,28 +838,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5091 HIJOS DE GRAU</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>-11.886214</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.132396</v>
-      </c>
-      <c r="I8" t="n">
-        <v>483</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.888391</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.128991</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -837,28 +895,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>144621</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5093 ANTONIO RAYMONDI</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>-11.885733</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.12378</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1489</v>
-      </c>
-      <c r="J9" t="n">
-        <v>57</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+          <t>NUESTRA SEÑORA DE BELEN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.873055</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.119737</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -884,28 +952,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144635</t>
+          <t>144701</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5094 NACIONES UNIDAS</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>-11.827088</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.129217</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1094</v>
-      </c>
-      <c r="J10" t="n">
-        <v>46</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+          <t>POLITECNICO VILLA LOS REYES</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.8291</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.1267</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -931,28 +1009,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>144678</t>
+          <t>144782</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LICEO NAVAL CAPITAN DE CORBETA MANUEL CLAVERO MUGA</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>-11.888391</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.128991</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1018</v>
-      </c>
-      <c r="J11" t="n">
-        <v>79</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+          <t>5121 PEDRO PLANAS SILVA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.825204</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.1362</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -978,28 +1066,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>144697</t>
+          <t>145140</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE BELEN</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-11.873055</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.119737</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1243</v>
-      </c>
-      <c r="J12" t="n">
-        <v>53</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+          <t>FE Y ALEGRIA 43</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.8223</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.1308</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1025,28 +1123,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>144701</t>
+          <t>319885</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>POLITECNICO VILLA LOS REYES</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>-11.8291</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.1267</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1218</v>
-      </c>
-      <c r="J13" t="n">
-        <v>66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+          <t>SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.82674</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.12656</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1072,28 +1180,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>144782</t>
+          <t>506472</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5121 PEDRO PLANAS SILVA</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>-11.825204</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.1362</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1184</v>
-      </c>
-      <c r="J14" t="n">
-        <v>53</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+          <t>5127 MARTIR JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.838755</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.123463</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1119,28 +1237,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>145140</t>
+          <t>593959</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 43</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>-11.8223</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.13079999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1263</v>
-      </c>
-      <c r="J15" t="n">
-        <v>64</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+          <t>5130-1 LOS LICENCIADOS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.8787</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.13167</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1166,28 +1294,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>145381</t>
+          <t>594124</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 29</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>-11.8748</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.1071</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1129</v>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.938141</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.136459</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1213,263 +1351,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>319885</t>
+          <t>595171</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>-11.82674</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.12656</v>
-      </c>
-      <c r="I17" t="n">
-        <v>532</v>
-      </c>
-      <c r="J17" t="n">
-        <v>31</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>070106</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>320105</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>3720 NUESTRA SEÑORA DE LA MISERICORDIA</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>-11.825532</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.12359600000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>921</v>
-      </c>
-      <c r="J18" t="n">
-        <v>44</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>070106</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>506472</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>5127 MARTIR JOSE OLAYA</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>-11.838755</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.123463</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1940</v>
-      </c>
-      <c r="J19" t="n">
-        <v>80</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>070106</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>593959</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>5130-1 LOS LICENCIADOS</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>-11.8787</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.13167</v>
-      </c>
-      <c r="I20" t="n">
-        <v>528</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>070106</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>594124</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>5130-3 VICTOR RAUL HAYA DE LA TORRE</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>-11.938141</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.136459</v>
-      </c>
-      <c r="I21" t="n">
-        <v>573</v>
-      </c>
-      <c r="J21" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>070106</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>595171</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>5141 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.837874</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.124257</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1141</v>
-      </c>
-      <c r="J22" t="n">
-        <v>45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.837874</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.124257</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
